--- a/ch_07/ch_07.xlsx
+++ b/ch_07/ch_07.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7AE34CC-4D84-4317-8E4D-1FED0537283C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" activeTab="1" xr2:uid="{127BCBE3-2501-4C38-9896-5064F2DA9264}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" activeTab="0" xr2:uid="{127BCBE3-2501-4C38-9896-5064F2DA9264}"/>
   </bookViews>
   <sheets>
     <sheet name="AirPassengers" sheetId="1" r:id="rId1"/>
